--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -934,7 +934,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117878218</v>
+        <v>117878228</v>
       </c>
       <c r="B4" t="n">
         <v>97753</v>
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468240</v>
+        <v>468233</v>
       </c>
       <c r="R4" t="n">
-        <v>6546901</v>
+        <v>6546797</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1156,7 +1156,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117878228</v>
+        <v>117878218</v>
       </c>
       <c r="B6" t="n">
         <v>97753</v>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468233</v>
+        <v>468240</v>
       </c>
       <c r="R6" t="n">
-        <v>6546797</v>
+        <v>6546901</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117878228</v>
+        <v>117878230</v>
       </c>
       <c r="B4" t="n">
-        <v>97753</v>
+        <v>108705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,25 +946,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117878230</v>
+        <v>117878218</v>
       </c>
       <c r="B5" t="n">
-        <v>108703</v>
+        <v>97755</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,25 +1057,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468233</v>
+        <v>468240</v>
       </c>
       <c r="R5" t="n">
-        <v>6546797</v>
+        <v>6546901</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117878218</v>
+        <v>117878228</v>
       </c>
       <c r="B6" t="n">
-        <v>97753</v>
+        <v>97755</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468240</v>
+        <v>468233</v>
       </c>
       <c r="R6" t="n">
-        <v>6546901</v>
+        <v>6546797</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1265,6 +1265,351 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120093195</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>468174</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6547107</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120093876</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svartå Åtorpskorset N3, Atlasruta 09E9e (Edsbacken), Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>468213</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6547054</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack och även äldre ringhack. på tall</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120093168</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>468163</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6547221</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska hackringar på en tall</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120093195</v>
+        <v>120093168</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1311,14 +1311,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468174</v>
+        <v>468163</v>
       </c>
       <c r="R7" t="n">
-        <v>6547107</v>
+        <v>6547221</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
+          <t>Färska hackringar på en tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120093876</v>
+        <v>120093195</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1426,14 +1426,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N3, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468213</v>
+        <v>468174</v>
       </c>
       <c r="R8" t="n">
-        <v>6547054</v>
+        <v>6547107</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack och även äldre ringhack. på tall</t>
+          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,7 +1497,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120093168</v>
+        <v>120093876</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1541,14 +1541,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N3, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468163</v>
+        <v>468213</v>
       </c>
       <c r="R9" t="n">
-        <v>6547221</v>
+        <v>6547054</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall</t>
+          <t>Färska ringhack och även äldre ringhack. på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120093168</v>
+        <v>120093195</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1311,14 +1311,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468163</v>
+        <v>468174</v>
       </c>
       <c r="R7" t="n">
-        <v>6547221</v>
+        <v>6547107</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall</t>
+          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120093195</v>
+        <v>120093876</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1426,14 +1426,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N3, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468174</v>
+        <v>468213</v>
       </c>
       <c r="R8" t="n">
-        <v>6547107</v>
+        <v>6547054</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
+          <t>Färska ringhack och även äldre ringhack. på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,7 +1497,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120093876</v>
+        <v>120093168</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1541,14 +1541,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N3, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468213</v>
+        <v>468163</v>
       </c>
       <c r="R9" t="n">
-        <v>6547054</v>
+        <v>6547221</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack och även äldre ringhack. på tall</t>
+          <t>Färska hackringar på en tall</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120093195</v>
+        <v>120093168</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1311,14 +1311,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468174</v>
+        <v>468163</v>
       </c>
       <c r="R7" t="n">
-        <v>6547107</v>
+        <v>6547221</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
+          <t>Färska hackringar på en tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1497,7 +1497,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120093168</v>
+        <v>120093195</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1541,14 +1541,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468163</v>
+        <v>468174</v>
       </c>
       <c r="R9" t="n">
-        <v>6547221</v>
+        <v>6547107</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall</t>
+          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -1270,7 +1270,7 @@
         <v>120093168</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120093876</v>
+        <v>120093195</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,14 +1426,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N3, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468213</v>
+        <v>468174</v>
       </c>
       <c r="R8" t="n">
-        <v>6547054</v>
+        <v>6547107</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack och även äldre ringhack. på tall</t>
+          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120093195</v>
+        <v>120093876</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1541,14 +1541,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N3, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468174</v>
+        <v>468213</v>
       </c>
       <c r="R9" t="n">
-        <v>6547107</v>
+        <v>6547054</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
+          <t>Färska ringhack och även äldre ringhack. på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120093168</v>
+        <v>120093195</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1311,14 +1311,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468163</v>
+        <v>468174</v>
       </c>
       <c r="R7" t="n">
-        <v>6547221</v>
+        <v>6547107</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall</t>
+          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120093195</v>
+        <v>120093168</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1426,14 +1426,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468174</v>
+        <v>468163</v>
       </c>
       <c r="R8" t="n">
-        <v>6547107</v>
+        <v>6547221</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
+          <t>Färska hackringar på en tall</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120093195</v>
+        <v>120093876</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1311,14 +1311,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N3, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468174</v>
+        <v>468213</v>
       </c>
       <c r="R7" t="n">
-        <v>6547107</v>
+        <v>6547054</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
+          <t>Färska ringhack och även äldre ringhack. på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1497,7 +1497,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120093876</v>
+        <v>120093195</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1541,14 +1541,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N3, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468213</v>
+        <v>468174</v>
       </c>
       <c r="R9" t="n">
-        <v>6547054</v>
+        <v>6547107</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack och även äldre ringhack. på tall</t>
+          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -1382,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120093168</v>
+        <v>120093195</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1426,14 +1426,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468163</v>
+        <v>468174</v>
       </c>
       <c r="R8" t="n">
-        <v>6547221</v>
+        <v>6547107</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall</t>
+          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,7 +1497,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120093195</v>
+        <v>120093168</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1541,14 +1541,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468174</v>
+        <v>468163</v>
       </c>
       <c r="R9" t="n">
-        <v>6547107</v>
+        <v>6547221</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
+          <t>Färska hackringar på en tall</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120093876</v>
+        <v>120093168</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1311,14 +1311,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N3, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468213</v>
+        <v>468163</v>
       </c>
       <c r="R7" t="n">
-        <v>6547054</v>
+        <v>6547221</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska ringhack och även äldre ringhack. på tall</t>
+          <t>Färska hackringar på en tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1497,7 +1497,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120093168</v>
+        <v>120093876</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1541,14 +1541,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N3, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468163</v>
+        <v>468213</v>
       </c>
       <c r="R9" t="n">
-        <v>6547221</v>
+        <v>6547054</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall</t>
+          <t>Färska ringhack och även äldre ringhack. på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120093168</v>
+        <v>120093195</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1311,14 +1311,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468163</v>
+        <v>468174</v>
       </c>
       <c r="R7" t="n">
-        <v>6547221</v>
+        <v>6547107</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall</t>
+          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120093195</v>
+        <v>120093876</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1426,14 +1426,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N3, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468174</v>
+        <v>468213</v>
       </c>
       <c r="R8" t="n">
-        <v>6547107</v>
+        <v>6547054</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
+          <t>Färska ringhack och även äldre ringhack. på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,7 +1497,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120093876</v>
+        <v>120093168</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1541,14 +1541,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N3, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468213</v>
+        <v>468163</v>
       </c>
       <c r="R9" t="n">
-        <v>6547054</v>
+        <v>6547221</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack och även äldre ringhack. på tall</t>
+          <t>Färska hackringar på en tall</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120093195</v>
+        <v>120093168</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1311,14 +1311,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468174</v>
+        <v>468163</v>
       </c>
       <c r="R7" t="n">
-        <v>6547107</v>
+        <v>6547221</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
+          <t>Färska hackringar på en tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1497,7 +1497,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120093168</v>
+        <v>120093195</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1541,14 +1541,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468163</v>
+        <v>468174</v>
       </c>
       <c r="R9" t="n">
-        <v>6547221</v>
+        <v>6547107</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall</t>
+          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1610,6 +1610,118 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128525023</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NV om Svartå Åtorpkorset, NV om Svartå Åtorpkorset, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>468222</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6547074</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall vid p-ficka</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -1615,7 +1615,7 @@
         <v>128525023</v>
       </c>
       <c r="B10" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -1615,7 +1615,7 @@
         <v>128525023</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1722,6 +1722,240 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128901083</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58573</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Edsbacken N, Edsbacken N, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>468161</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6546671</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128901289</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57557</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Anderstorp S, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>468192</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6546797</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Strax sör om Anderstorp</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -1615,7 +1615,7 @@
         <v>128525023</v>
       </c>
       <c r="B10" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>128901083</v>
       </c>
       <c r="B11" t="n">
-        <v>58573</v>
+        <v>58577</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>128901289</v>
       </c>
       <c r="B12" t="n">
-        <v>57557</v>
+        <v>57561</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -1615,7 +1615,7 @@
         <v>128525023</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>128901083</v>
       </c>
       <c r="B11" t="n">
-        <v>58577</v>
+        <v>58580</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>128901289</v>
       </c>
       <c r="B12" t="n">
-        <v>57561</v>
+        <v>57564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1727,7 +1727,7 @@
         <v>128901083</v>
       </c>
       <c r="B11" t="n">
-        <v>58580</v>
+        <v>58582</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>128901289</v>
       </c>
       <c r="B12" t="n">
-        <v>57564</v>
+        <v>57566</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,6 +1955,128 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129263257</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56915</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NV om Svartå Åtorpkorset, NV om Svartå Åtorpkorset, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>468227</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6547145</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Åt grus på vägen</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -1727,7 +1727,7 @@
         <v>128901083</v>
       </c>
       <c r="B11" t="n">
-        <v>58582</v>
+        <v>58584</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>128901289</v>
       </c>
       <c r="B12" t="n">
-        <v>57566</v>
+        <v>57568</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>129263257</v>
       </c>
       <c r="B13" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -1961,7 +1961,7 @@
         <v>129263257</v>
       </c>
       <c r="B13" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1961,7 +1961,7 @@
         <v>129263257</v>
       </c>
       <c r="B13" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,6 +2077,357 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129722287</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>468151</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6547327</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran med rinnande kåda. Ca4 m fr vägen i storskogen.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129722206</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>468157</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6547337</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack av tretåig hackspett på gran.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129722214</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NV om Svartå Åtorpkorset, NV om Svartå Åtorpkorset, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>468145</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6547342</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska spår på gran I skogens kant</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -1961,7 +1961,7 @@
         <v>129263257</v>
       </c>
       <c r="B13" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>129722287</v>
       </c>
       <c r="B14" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>129722206</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>129722214</v>
       </c>
       <c r="B16" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1836,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128901289</v>
+        <v>129263257</v>
       </c>
       <c r="B12" t="n">
-        <v>57568</v>
+        <v>56926</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,44 +1847,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102621</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Anderstorp S, Skogskärr, Nrk</t>
+          <t>NV om Svartå Åtorpkorset, NV om Svartå Åtorpkorset, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468192</v>
+        <v>468227</v>
       </c>
       <c r="R12" t="n">
-        <v>6546797</v>
+        <v>6547145</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1911,27 +1911,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Strax sör om Anderstorp</t>
+          <t>Åt grus på vägen</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,55 +1958,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129263257</v>
+        <v>129722287</v>
       </c>
       <c r="B13" t="n">
-        <v>56926</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>NV om Svartå Åtorpkorset, NV om Svartå Åtorpkorset, Nrk</t>
+          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468227</v>
+        <v>468151</v>
       </c>
       <c r="R13" t="n">
-        <v>6547145</v>
+        <v>6547327</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2033,27 +2028,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Åt grus på vägen</t>
+          <t>Färska ringhack på gran med rinnande kåda. Ca4 m fr vägen i storskogen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2068,19 +2063,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129722287</v>
+        <v>129722206</v>
       </c>
       <c r="B14" t="n">
         <v>57736</v>
@@ -2120,10 +2115,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468151</v>
+        <v>468157</v>
       </c>
       <c r="R14" t="n">
-        <v>6547327</v>
+        <v>6547337</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2155,7 +2150,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2165,12 +2160,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran med rinnande kåda. Ca4 m fr vägen i storskogen.</t>
+          <t>Färska ringhack av tretåig hackspett på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2197,7 +2192,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129722206</v>
+        <v>129722214</v>
       </c>
       <c r="B15" t="n">
         <v>57736</v>
@@ -2233,14 +2228,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>NV om Svartå Åtorpkorset, NV om Svartå Åtorpkorset, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468157</v>
+        <v>468145</v>
       </c>
       <c r="R15" t="n">
-        <v>6547337</v>
+        <v>6547342</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2272,7 +2267,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2282,12 +2277,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretåig hackspett på gran.</t>
+          <t>Färska spår på gran I skogens kant</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2302,132 +2297,15 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>129722214</v>
-      </c>
-      <c r="B16" t="n">
-        <v>57736</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>NV om Svartå Åtorpkorset, NV om Svartå Åtorpkorset, Nrk</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>468145</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6547342</v>
-      </c>
-      <c r="S16" t="n">
-        <v>20</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Närke</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Nysund</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska spår på gran I skogens kant</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>David Tverling</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>David Tverling</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -1961,7 +1961,7 @@
         <v>129722287</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>129722206</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>129722214</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -1961,7 +1961,7 @@
         <v>129722287</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>129722206</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>129722214</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6996059</v>
+        <v>6995594</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468239.072079769</v>
+        <v>468239</v>
       </c>
       <c r="R2" t="n">
-        <v>6547033.169971243</v>
+        <v>6547033</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2012-10-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-10-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,69 +791,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117024673</v>
+        <v>115630946</v>
       </c>
       <c r="B3" t="n">
-        <v>56494</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NV om Svartå Åtorpkorset, Nrk</t>
+          <t>Edsbacken, Edsbacken, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468188</v>
+        <v>468218</v>
       </c>
       <c r="R3" t="n">
-        <v>6547209</v>
+        <v>6546697</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,22 +861,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack på 2 tallar några meter in från grusvägen, väl synliga fr vägen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,27 +896,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117878230</v>
+        <v>120093072</v>
       </c>
       <c r="B4" t="n">
-        <v>108708</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -950,42 +919,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rultamon, Nrk</t>
+          <t>Svartå Åtorpskorset O, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468233</v>
+        <v>468331</v>
       </c>
       <c r="R4" t="n">
-        <v>6546797</v>
+        <v>6546835</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1012,12 +981,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska hackringar på en tall som står söder om en gammal tall med bohål i</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,77 +1000,71 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117878218</v>
+        <v>120093168</v>
       </c>
       <c r="B5" t="n">
-        <v>97757</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rultamon, Nrk</t>
+          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468240</v>
+        <v>468163</v>
       </c>
       <c r="R5" t="n">
-        <v>6546901</v>
+        <v>6547221</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1123,12 +1091,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska hackringar på en tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,77 +1110,71 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117878228</v>
+        <v>120093195</v>
       </c>
       <c r="B6" t="n">
-        <v>97757</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rultamon, Nrk</t>
+          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468233</v>
+        <v>468174</v>
       </c>
       <c r="R6" t="n">
-        <v>6546797</v>
+        <v>6547107</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1234,12 +1201,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,34 +1220,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120093168</v>
+        <v>120093303</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,14 +1277,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset V, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468163</v>
+        <v>468096</v>
       </c>
       <c r="R7" t="n">
-        <v>6547221</v>
+        <v>6546799</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1355,7 +1321,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall</t>
+          <t>Barkfläkning på gran i hyggeskant</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,12 +1351,7 @@
         <v>120093876</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,15 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120093195</v>
+        <v>128525023</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,27 +1487,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N2, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>NV om Svartå Åtorpkorset, NV om Svartå Åtorpkorset, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468174</v>
+        <v>468222</v>
       </c>
       <c r="R9" t="n">
-        <v>6547107</v>
+        <v>6547074</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1575,17 +1523,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall nära körväg, på norra sidan av körvägen</t>
+          <t>Färska ringhack på tall vid p-ficka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,22 +1558,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128525023</v>
+        <v>128525158</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,14 +1601,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>NV om Svartå Åtorpkorset, NV om Svartå Åtorpkorset, Nrk</t>
+          <t>Edsbacken N, Edsbacken N, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468222</v>
+        <v>468235</v>
       </c>
       <c r="R10" t="n">
-        <v>6547074</v>
+        <v>6546696</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1682,7 +1640,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,12 +1650,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall vid p-ficka</t>
+          <t>Färska ringhack på tall (tills m äldre ringhack) Ö sidan av vägen, 5m från vägen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,50 +1682,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128901083</v>
+        <v>129722206</v>
       </c>
       <c r="B11" t="n">
-        <v>58584</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208250</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>parning/parningsceremonier</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Edsbacken N, Edsbacken N, Nrk</t>
+          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468161</v>
+        <v>468157</v>
       </c>
       <c r="R11" t="n">
-        <v>6546671</v>
+        <v>6547337</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1794,22 +1752,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack av tretåig hackspett på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,55 +1787,50 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129263257</v>
+        <v>129722214</v>
       </c>
       <c r="B12" t="n">
-        <v>56926</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1881,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468227</v>
+        <v>468145</v>
       </c>
       <c r="R12" t="n">
-        <v>6547145</v>
+        <v>6547342</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1911,27 +1869,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Åt grus på vägen</t>
+          <t>Färska spår på gran I skogens kant</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,7 +1919,7 @@
         <v>129722287</v>
       </c>
       <c r="B13" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,53 +2033,64 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129722206</v>
+        <v>117024673</v>
       </c>
       <c r="B14" t="n">
-        <v>57740</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset N, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>NV om Svartå Åtorpkorset, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468157</v>
+        <v>468188</v>
       </c>
       <c r="R14" t="n">
-        <v>6547337</v>
+        <v>6547209</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2145,27 +2114,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack av tretåig hackspett på gran.</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2180,50 +2144,55 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129722214</v>
+        <v>129263257</v>
       </c>
       <c r="B15" t="n">
-        <v>57740</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2232,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468145</v>
+        <v>468227</v>
       </c>
       <c r="R15" t="n">
-        <v>6547342</v>
+        <v>6547145</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2262,27 +2231,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska spår på gran I skogens kant</t>
+          <t>Åt grus på vägen</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,6 +2275,759 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128901083</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Edsbacken N, Edsbacken N, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>468161</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6546671</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>117878207</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Edsbacketorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>468152</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6546931</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>117878218</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Rultamon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>468240</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6546901</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>117878228</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rultamon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>468233</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6546797</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>117878302</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Edsbacken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>468187</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6546639</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>117878230</v>
+      </c>
+      <c r="B21" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rultamon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>468233</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6546797</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>117878298</v>
+      </c>
+      <c r="B22" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Edsbacken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>468187</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6546639</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6995594</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115630946</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120093168</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120093195</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,6 +1260,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120093303</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1345,6 +1375,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120093876</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1457,6 +1492,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128525023</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1569,6 +1609,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128525158</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1686,6 +1731,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129722206</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1803,6 +1853,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129722214</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1920,6 +1975,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129722287</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2043,6 +2103,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117024673</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2165,6 +2230,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129263257</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2277,6 +2347,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128901083</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2383,6 +2458,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117878207</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2489,6 +2569,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117878218</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2595,6 +2680,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117878228</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2701,6 +2791,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117878302</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2807,6 +2902,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117878230</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2918,6 +3018,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117878298</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3028,8 +3133,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120093072</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>